--- a/reference/configurations.xlsx
+++ b/reference/configurations.xlsx
@@ -135,7 +135,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -193,6 +193,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="9" min="1" max="1"/>
@@ -558,6 +560,21 @@
       <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Stockout warnings below this many units are suppressed (kills the 0.16-unit noise).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>sales_recency_prompt_days</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>v2.9: if the sales window's END is more than this many days behind the stock anchor date, the app asks you to confirm before planning (older window = deliberate choice, acknowledged, flagged). Not a hard stop.</t>
         </is>
       </c>
     </row>
@@ -1513,62 +1530,61 @@
     </row>
     <row r="35" ht="15" customHeight="1" s="10"/>
     <row r="36" ht="15" customHeight="1" s="10">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>TAB: Demand_Map (added v2.8)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="10">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Maps demand states WITHOUT a local FC to the region that serves them. A state that has its own</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>FCs maps to itself automatically from the registration file and must NOT appear here (a row naming</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>an FC state is a validation error). Columns: Demand state (spelled out, as normalized from the</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>sales file) | Serving state code (must be a state with registered FCs) | Note. A sales state that</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>is neither an FC state nor listed here produces a NAMED WARNING with its unit count - visible,</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>never silently dropped. If a state later gains its own FC, its row here turns into a warning</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>("state now has its own FCs; row ignored - delete it"), not an error.</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>

--- a/reference/configurations.xlsx
+++ b/reference/configurations.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="9" min="1" max="1"/>
@@ -521,63 +521,34 @@
     <row r="5" ht="23.85" customHeight="1" s="10">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>ixd_transfer_days</t>
+          <t>min_stockout_deficit_units</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Assumed days for stock at BLR4 IXD to reach a regional FC after Amazon redistributes it. Used to time IXD-offset arrivals.</t>
+          <t>Stockout warnings below this many units are suppressed (kills the 0.16-unit noise).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23.85" customHeight="1" s="10">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>ixd_confidence</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>0 to 1. How much of the IXD proportional-split offset to apply. 1.0 = full offset (trust the split), 0 = IXD stock is informational only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="10">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>min_stockout_deficit_units</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Stockout warnings below this many units are suppressed (kills the 0.16-unit noise).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>sales_recency_prompt_days</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B6" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>v2.9: if the sales window's END is more than this many days behind the stock anchor date, the app asks you to confirm before planning (older window = deliberate choice, acknowledged, flagged). Not a hard stop.</t>
         </is>
       </c>
     </row>
+    <row r="7" ht="15" customHeight="1" s="10"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/reference/configurations.xlsx
+++ b/reference/configurations.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="9" min="1" max="1"/>
@@ -548,7 +548,40 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="10"/>
+    <row r="7" ht="15" customHeight="1" s="10">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ixd_region_label</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BLR4 IXD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Label of the cross-dock hub region. If Amazon moves the IXD to another FC, update FC_Types AND this label (and rename the matching column in the master template + regenerate the stock workbook).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ignore_region_label</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>YSXA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Label of the ignored/SellerFlex region (shown on stock tabs, never planned).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
